--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/106.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/106.xlsx
@@ -426,13 +426,13 @@
         <v>-8.281136406365256</v>
       </c>
       <c r="E2">
-        <v>-16.46014015605389</v>
+        <v>-18.20676352386433</v>
       </c>
       <c r="F2">
-        <v>-1.698601469751409</v>
+        <v>-2.614792384595718</v>
       </c>
       <c r="G2">
-        <v>-11.89368220911002</v>
+        <v>-13.94199789247962</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.459651794389739</v>
       </c>
       <c r="E3">
-        <v>-15.70777042747152</v>
+        <v>-20.53378329134185</v>
       </c>
       <c r="F3">
-        <v>-1.636733193538522</v>
+        <v>-2.096120904109044</v>
       </c>
       <c r="G3">
-        <v>-12.40813509375067</v>
+        <v>-13.98782015155726</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.588981266027876</v>
       </c>
       <c r="E4">
-        <v>-17.78742683075405</v>
+        <v>-19.67092332544633</v>
       </c>
       <c r="F4">
-        <v>-1.500055057178812</v>
+        <v>-2.315988665262297</v>
       </c>
       <c r="G4">
-        <v>-11.69454815388888</v>
+        <v>-14.12055704791226</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.661061232497346</v>
       </c>
       <c r="E5">
-        <v>-16.48981071775214</v>
+        <v>-21.01637370939126</v>
       </c>
       <c r="F5">
-        <v>-2.112210284173619</v>
+        <v>-2.14153117676311</v>
       </c>
       <c r="G5">
-        <v>-11.82757215713032</v>
+        <v>-13.43671930331917</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.71053116311786</v>
       </c>
       <c r="E6">
-        <v>-17.34533908422924</v>
+        <v>-22.04259837511349</v>
       </c>
       <c r="F6">
-        <v>-1.258643944980952</v>
+        <v>-2.109084025595453</v>
       </c>
       <c r="G6">
-        <v>-11.42181629908939</v>
+        <v>-12.79093880698329</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.770175153815508</v>
       </c>
       <c r="E7">
-        <v>-18.93496931514177</v>
+        <v>-22.09472563941578</v>
       </c>
       <c r="F7">
-        <v>-1.529792618571912</v>
+        <v>-2.307027386698812</v>
       </c>
       <c r="G7">
-        <v>-11.85317224773711</v>
+        <v>-12.7972485960421</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.852499122370887</v>
       </c>
       <c r="E8">
-        <v>-19.08253869762972</v>
+        <v>-23.21726641880715</v>
       </c>
       <c r="F8">
-        <v>-1.846403751963313</v>
+        <v>-2.071801693897656</v>
       </c>
       <c r="G8">
-        <v>-11.68241747778361</v>
+        <v>-12.99009911197691</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.978744916083194</v>
       </c>
       <c r="E9">
-        <v>-19.53044553325439</v>
+        <v>-23.10054500125944</v>
       </c>
       <c r="F9">
-        <v>-1.339560529621213</v>
+        <v>-1.768166107503706</v>
       </c>
       <c r="G9">
-        <v>-11.09806801148366</v>
+        <v>-13.05378434122417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.143866462250198</v>
       </c>
       <c r="E10">
-        <v>-20.07431073310159</v>
+        <v>-23.92070598573664</v>
       </c>
       <c r="F10">
-        <v>-0.9976195777870084</v>
+        <v>-2.05488063296067</v>
       </c>
       <c r="G10">
-        <v>-10.98967941971052</v>
+        <v>-12.80846053011073</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.331683744991254</v>
       </c>
       <c r="E11">
-        <v>-20.75132212572232</v>
+        <v>-23.41812235494336</v>
       </c>
       <c r="F11">
-        <v>-1.081958148168234</v>
+        <v>-2.336219053973467</v>
       </c>
       <c r="G11">
-        <v>-11.28345046714917</v>
+        <v>-13.26758873803759</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.527071565174614</v>
       </c>
       <c r="E12">
-        <v>-21.34527677656836</v>
+        <v>-24.65209076576746</v>
       </c>
       <c r="F12">
-        <v>-0.9351267125524109</v>
+        <v>-1.793915079852326</v>
       </c>
       <c r="G12">
-        <v>-11.18439695071265</v>
+        <v>-12.95528863245276</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.6918803908644</v>
       </c>
       <c r="E13">
-        <v>-22.44890212002969</v>
+        <v>-25.40427935538953</v>
       </c>
       <c r="F13">
-        <v>-0.7717295856154027</v>
+        <v>-0.8863441562015479</v>
       </c>
       <c r="G13">
-        <v>-10.85391559646694</v>
+        <v>-12.63796497666042</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.807406103935088</v>
       </c>
       <c r="E14">
-        <v>-22.65089017466782</v>
+        <v>-25.14363850540405</v>
       </c>
       <c r="F14">
-        <v>-0.7103657851508209</v>
+        <v>-1.183550783182371</v>
       </c>
       <c r="G14">
-        <v>-11.4197524107285</v>
+        <v>-11.99251588370205</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.843769591064733</v>
       </c>
       <c r="E15">
-        <v>-23.95698359101209</v>
+        <v>-26.30018812459302</v>
       </c>
       <c r="F15">
-        <v>-0.2389137317259272</v>
+        <v>-1.201503989903245</v>
       </c>
       <c r="G15">
-        <v>-11.09697536470436</v>
+        <v>-11.98368611648558</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.779621792517801</v>
       </c>
       <c r="E16">
-        <v>-25.40453747840796</v>
+        <v>-27.64908467725779</v>
       </c>
       <c r="F16">
-        <v>0.09000528453626973</v>
+        <v>-1.052933811108945</v>
       </c>
       <c r="G16">
-        <v>-10.08404586319598</v>
+        <v>-11.47813190471414</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.60832435253262</v>
       </c>
       <c r="E17">
-        <v>-25.33895158935487</v>
+        <v>-29.57226418967928</v>
       </c>
       <c r="F17">
-        <v>0.457846799953807</v>
+        <v>-0.791097643860258</v>
       </c>
       <c r="G17">
-        <v>-10.14633657328048</v>
+        <v>-11.31435629301758</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.317586795239077</v>
       </c>
       <c r="E18">
-        <v>-26.28168025132367</v>
+        <v>-30.15859062605941</v>
       </c>
       <c r="F18">
-        <v>0.7914361516329875</v>
+        <v>-0.8071654863723601</v>
       </c>
       <c r="G18">
-        <v>-10.31330809477594</v>
+        <v>-10.84557801248439</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.920129797809921</v>
       </c>
       <c r="E19">
-        <v>-26.19323462547986</v>
+        <v>-30.71591671489441</v>
       </c>
       <c r="F19">
-        <v>1.264250041068084</v>
+        <v>0.03015491131660265</v>
       </c>
       <c r="G19">
-        <v>-9.973724631924332</v>
+        <v>-10.43310221268971</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.424967459699655</v>
       </c>
       <c r="E20">
-        <v>-28.43366091298271</v>
+        <v>-31.99250712307871</v>
       </c>
       <c r="F20">
-        <v>1.333922366582744</v>
+        <v>-0.004171805488006062</v>
       </c>
       <c r="G20">
-        <v>-10.28737331957009</v>
+        <v>-9.700891059256504</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.851725711903044</v>
       </c>
       <c r="E21">
-        <v>-28.40038568597435</v>
+        <v>-31.29821733788171</v>
       </c>
       <c r="F21">
-        <v>1.712289118220252</v>
+        <v>0.1246550646279703</v>
       </c>
       <c r="G21">
-        <v>-9.050805600234639</v>
+        <v>-9.901596819604618</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.232008458253254</v>
       </c>
       <c r="E22">
-        <v>-28.67684902414262</v>
+        <v>-32.97456331756712</v>
       </c>
       <c r="F22">
-        <v>1.713781836280097</v>
+        <v>0.439440476263602</v>
       </c>
       <c r="G22">
-        <v>-9.432211513082933</v>
+        <v>-10.81862933981667</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.587243991150828</v>
       </c>
       <c r="E23">
-        <v>-29.98347227194579</v>
+        <v>-33.15462676529711</v>
       </c>
       <c r="F23">
-        <v>1.823121363245215</v>
+        <v>0.7361144630044253</v>
       </c>
       <c r="G23">
-        <v>-8.87193308814307</v>
+        <v>-9.354443280902535</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.95419164059604</v>
       </c>
       <c r="E24">
-        <v>-30.47984057216354</v>
+        <v>-32.5478203052173</v>
       </c>
       <c r="F24">
-        <v>2.395607732054759</v>
+        <v>1.312731071684328</v>
       </c>
       <c r="G24">
-        <v>-9.581717092217472</v>
+        <v>-10.42356698283796</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.353991697682749</v>
       </c>
       <c r="E25">
-        <v>-30.0317163697865</v>
+        <v>-31.68447126412895</v>
       </c>
       <c r="F25">
-        <v>1.978801419457743</v>
+        <v>0.8890161749479637</v>
       </c>
       <c r="G25">
-        <v>-8.544788736223312</v>
+        <v>-8.899685660092853</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.804083746405736</v>
       </c>
       <c r="E26">
-        <v>-30.4060151246535</v>
+        <v>-34.1161191593167</v>
       </c>
       <c r="F26">
-        <v>2.522273391616831</v>
+        <v>1.275770974906219</v>
       </c>
       <c r="G26">
-        <v>-8.838759938177084</v>
+        <v>-9.289025566671885</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.320506833324061</v>
       </c>
       <c r="E27">
-        <v>-29.5742250189246</v>
+        <v>-32.9407197670708</v>
       </c>
       <c r="F27">
-        <v>2.194017897644277</v>
+        <v>1.433813534951531</v>
       </c>
       <c r="G27">
-        <v>-7.587384065943856</v>
+        <v>-10.6092381860007</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.89926486759319</v>
       </c>
       <c r="E28">
-        <v>-30.5960049874083</v>
+        <v>-32.74711618205787</v>
       </c>
       <c r="F28">
-        <v>2.123778968826101</v>
+        <v>0.8611880004183171</v>
       </c>
       <c r="G28">
-        <v>-8.315073696068147</v>
+        <v>-10.00365593498959</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.54428637293938</v>
       </c>
       <c r="E29">
-        <v>-28.78080920193671</v>
+        <v>-32.92658413545585</v>
       </c>
       <c r="F29">
-        <v>2.050024448750444</v>
+        <v>1.091262076341463</v>
       </c>
       <c r="G29">
-        <v>-9.027033150036463</v>
+        <v>-9.583705512482496</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.244296461924562</v>
       </c>
       <c r="E30">
-        <v>-29.93124764545233</v>
+        <v>-33.16048208218903</v>
       </c>
       <c r="F30">
-        <v>1.695062389711634</v>
+        <v>0.2811941378372012</v>
       </c>
       <c r="G30">
-        <v>-8.294014816099631</v>
+        <v>-9.928187839122359</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.985993550862616</v>
       </c>
       <c r="E31">
-        <v>-28.96276781603892</v>
+        <v>-32.50142156053471</v>
       </c>
       <c r="F31">
-        <v>1.90023077130221</v>
+        <v>0.8020624486760995</v>
       </c>
       <c r="G31">
-        <v>-8.263932576842642</v>
+        <v>-8.884713446117107</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.761419343755621</v>
       </c>
       <c r="E32">
-        <v>-28.02305511775922</v>
+        <v>-31.12053360324275</v>
       </c>
       <c r="F32">
-        <v>1.603246146785337</v>
+        <v>0.8072629392308749</v>
       </c>
       <c r="G32">
-        <v>-8.413513624073049</v>
+        <v>-9.258529893498405</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.553680260631165</v>
       </c>
       <c r="E33">
-        <v>-28.41677423340811</v>
+        <v>-32.10001988873181</v>
       </c>
       <c r="F33">
-        <v>1.8179092755468</v>
+        <v>0.3298383568317966</v>
       </c>
       <c r="G33">
-        <v>-8.361647354882907</v>
+        <v>-8.643484599509851</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.359580729644472</v>
       </c>
       <c r="E34">
-        <v>-28.54973023027331</v>
+        <v>-30.35723666687987</v>
       </c>
       <c r="F34">
-        <v>1.409572191276007</v>
+        <v>0.09527784305508859</v>
       </c>
       <c r="G34">
-        <v>-7.896314356987135</v>
+        <v>-8.416676721656353</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.174530872020152</v>
       </c>
       <c r="E35">
-        <v>-28.52454738631666</v>
+        <v>-30.9727876102685</v>
       </c>
       <c r="F35">
-        <v>1.316442157648869</v>
+        <v>-0.2715663180094781</v>
       </c>
       <c r="G35">
-        <v>-8.233187530830646</v>
+        <v>-9.169254417309034</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.997465309658046</v>
       </c>
       <c r="E36">
-        <v>-27.28897589569383</v>
+        <v>-30.36888843050161</v>
       </c>
       <c r="F36">
-        <v>1.248091906509077</v>
+        <v>0.2086780270287297</v>
       </c>
       <c r="G36">
-        <v>-7.747077838020471</v>
+        <v>-8.746905421841989</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.836014992636223</v>
       </c>
       <c r="E37">
-        <v>-26.64585560254651</v>
+        <v>-32.34582319363115</v>
       </c>
       <c r="F37">
-        <v>1.046682656192405</v>
+        <v>0.6197470669939563</v>
       </c>
       <c r="G37">
-        <v>-7.847860558218815</v>
+        <v>-9.862340284867422</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.691890637035629</v>
       </c>
       <c r="E38">
-        <v>-26.36306145771552</v>
+        <v>-30.37863370656612</v>
       </c>
       <c r="F38">
-        <v>0.9312297777946265</v>
+        <v>-0.1276267129968276</v>
       </c>
       <c r="G38">
-        <v>-7.958857721131711</v>
+        <v>-9.349104733425317</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.573156585667869</v>
       </c>
       <c r="E39">
-        <v>-26.36055721158927</v>
+        <v>-29.32316641993936</v>
       </c>
       <c r="F39">
-        <v>0.9031597199833624</v>
+        <v>0.1179775949940034</v>
       </c>
       <c r="G39">
-        <v>-7.453949910007477</v>
+        <v>-9.375282319026567</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.485455366907745</v>
       </c>
       <c r="E40">
-        <v>-25.56675647431073</v>
+        <v>-28.8414952821135</v>
       </c>
       <c r="F40">
-        <v>1.19586996870179</v>
+        <v>0.3294920992574264</v>
       </c>
       <c r="G40">
-        <v>-7.72557599314143</v>
+        <v>-8.794066419315888</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.430064405629413</v>
       </c>
       <c r="E41">
-        <v>-26.12683361110539</v>
+        <v>-27.17844943058862</v>
       </c>
       <c r="F41">
-        <v>0.9105802351776404</v>
+        <v>0.3530541816626556</v>
       </c>
       <c r="G41">
-        <v>-7.491113025389748</v>
+        <v>-9.258086928587881</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.413157327161335</v>
       </c>
       <c r="E42">
-        <v>-24.60371760641753</v>
+        <v>-26.97320087466498</v>
       </c>
       <c r="F42">
-        <v>0.6940980115996288</v>
+        <v>-0.2912773203590923</v>
       </c>
       <c r="G42">
-        <v>-7.04448955282593</v>
+        <v>-8.635117484533266</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.433108565910344</v>
       </c>
       <c r="E43">
-        <v>-23.19128203495114</v>
+        <v>-26.84472806706736</v>
       </c>
       <c r="F43">
-        <v>1.004717563566582</v>
+        <v>-0.352517694080657</v>
       </c>
       <c r="G43">
-        <v>-7.21006327393707</v>
+        <v>-8.277126368733169</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.48989532725743</v>
       </c>
       <c r="E44">
-        <v>-23.2433911853574</v>
+        <v>-25.7251987228911</v>
       </c>
       <c r="F44">
-        <v>0.7471450033401036</v>
+        <v>-0.4074152585989858</v>
       </c>
       <c r="G44">
-        <v>-8.146829060607621</v>
+        <v>-9.674539568912603</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.5831373449926</v>
       </c>
       <c r="E45">
-        <v>-22.99575158424794</v>
+        <v>-26.65628014971217</v>
       </c>
       <c r="F45">
-        <v>1.137662248041875</v>
+        <v>0.1118228251912031</v>
       </c>
       <c r="G45">
-        <v>-7.479589375272978</v>
+        <v>-9.737332305895698</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.706029740099988</v>
       </c>
       <c r="E46">
-        <v>-21.97028770215901</v>
+        <v>-26.71535862161624</v>
       </c>
       <c r="F46">
-        <v>1.166559016521132</v>
+        <v>-0.1670379489198197</v>
       </c>
       <c r="G46">
-        <v>-7.820331109335074</v>
+        <v>-9.275595526829077</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.859677225006917</v>
       </c>
       <c r="E47">
-        <v>-22.05645097710295</v>
+        <v>-26.11446182011644</v>
       </c>
       <c r="F47">
-        <v>0.9059496613959912</v>
+        <v>0.3433357752930117</v>
       </c>
       <c r="G47">
-        <v>-7.791604014582135</v>
+        <v>-9.309523357753736</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.040386092466486</v>
       </c>
       <c r="E48">
-        <v>-21.53597987397938</v>
+        <v>-25.45422389522012</v>
       </c>
       <c r="F48">
-        <v>0.437139271618625</v>
+        <v>0.1051991994384183</v>
       </c>
       <c r="G48">
-        <v>-7.081321264830697</v>
+        <v>-10.04139654536632</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.246337500346769</v>
       </c>
       <c r="E49">
-        <v>-20.03781576107378</v>
+        <v>-24.89256632099678</v>
       </c>
       <c r="F49">
-        <v>0.6854697367320691</v>
+        <v>-0.09991202480136452</v>
       </c>
       <c r="G49">
-        <v>-7.815015530408774</v>
+        <v>-8.204168407358917</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.480764150804796</v>
       </c>
       <c r="E50">
-        <v>-20.19594554494762</v>
+        <v>-23.12488102057667</v>
       </c>
       <c r="F50">
-        <v>0.5652595443400132</v>
+        <v>-0.08150570111115951</v>
       </c>
       <c r="G50">
-        <v>-7.988224654088741</v>
+        <v>-9.381365703797778</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.738649535418127</v>
       </c>
       <c r="E51">
-        <v>-19.86142717000101</v>
+        <v>-21.49468019102942</v>
       </c>
       <c r="F51">
-        <v>0.8120492460842504</v>
+        <v>-0.3686153578192597</v>
       </c>
       <c r="G51">
-        <v>-7.322993076348479</v>
+        <v>-7.803413130974577</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.024570900982932</v>
       </c>
       <c r="E52">
-        <v>-18.36664582717914</v>
+        <v>-22.37675447213948</v>
       </c>
       <c r="F52">
-        <v>0.6445417600945512</v>
+        <v>0.200516951376349</v>
       </c>
       <c r="G52">
-        <v>-7.768714212983449</v>
+        <v>-9.277203325393206</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.33684161384162</v>
       </c>
       <c r="E53">
-        <v>-18.24126143885476</v>
+        <v>-22.83290313045811</v>
       </c>
       <c r="F53">
-        <v>0.9214268779498971</v>
+        <v>-0.1674918942565538</v>
       </c>
       <c r="G53">
-        <v>-7.855637053314699</v>
+        <v>-9.146043055997522</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.671107194102031</v>
       </c>
       <c r="E54">
-        <v>-18.08895527255478</v>
+        <v>-23.17753358786385</v>
       </c>
       <c r="F54">
-        <v>0.7846186879079475</v>
+        <v>-0.1521737242439853</v>
       </c>
       <c r="G54">
-        <v>-8.225709626896672</v>
+        <v>-10.02361560573569</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.028142849600506</v>
       </c>
       <c r="E55">
-        <v>-16.31795512916105</v>
+        <v>-21.25994221236782</v>
       </c>
       <c r="F55">
-        <v>0.9172022041956196</v>
+        <v>0.3707464526516474</v>
       </c>
       <c r="G55">
-        <v>-7.556747300243321</v>
+        <v>-10.27049799708987</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.396624051058044</v>
       </c>
       <c r="E56">
-        <v>-16.7043924586056</v>
+        <v>-20.56962616311256</v>
       </c>
       <c r="F56">
-        <v>0.4016876318810145</v>
+        <v>-0.3308144681273099</v>
       </c>
       <c r="G56">
-        <v>-8.142602847239056</v>
+        <v>-8.903518126874285</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.774408631619382</v>
       </c>
       <c r="E57">
-        <v>-16.65629553617013</v>
+        <v>-20.45093938784553</v>
       </c>
       <c r="F57">
-        <v>1.07270830325356</v>
+        <v>0.2005368321940162</v>
       </c>
       <c r="G57">
-        <v>-8.249186767154498</v>
+        <v>-9.363952260981804</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.153361353342666</v>
       </c>
       <c r="E58">
-        <v>-15.54343210573316</v>
+        <v>-20.39682412345386</v>
       </c>
       <c r="F58">
-        <v>0.4840695984568281</v>
+        <v>-0.1060659662367621</v>
       </c>
       <c r="G58">
-        <v>-8.02019687696397</v>
+        <v>-9.825649665389712</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.522622223821253</v>
       </c>
       <c r="E59">
-        <v>-15.06899294089755</v>
+        <v>-20.7635897618091</v>
       </c>
       <c r="F59">
-        <v>0.5931954066320239</v>
+        <v>-0.4750440017309402</v>
       </c>
       <c r="G59">
-        <v>-8.396976267413448</v>
+        <v>-10.19651301336751</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.879561557378254</v>
       </c>
       <c r="E60">
-        <v>-15.0181879910055</v>
+        <v>-19.72023840738986</v>
       </c>
       <c r="F60">
-        <v>0.284876230942645</v>
+        <v>-0.2394488570681357</v>
       </c>
       <c r="G60">
-        <v>-8.671033735722949</v>
+        <v>-10.46513349755301</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.209996297723314</v>
       </c>
       <c r="E61">
-        <v>-14.34098187400244</v>
+        <v>-18.19152520882852</v>
       </c>
       <c r="F61">
-        <v>0.6582040236689234</v>
+        <v>-0.4871655019361054</v>
       </c>
       <c r="G61">
-        <v>-8.704174073473339</v>
+        <v>-10.57824048592863</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.510892966382174</v>
       </c>
       <c r="E62">
-        <v>-13.91367959511268</v>
+        <v>-18.43897914250365</v>
       </c>
       <c r="F62">
-        <v>0.2268706319290124</v>
+        <v>-0.5390386970668133</v>
       </c>
       <c r="G62">
-        <v>-8.067390686653464</v>
+        <v>-10.7928980003475</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.773978520877659</v>
       </c>
       <c r="E63">
-        <v>-13.43392400179206</v>
+        <v>-16.82545215425266</v>
       </c>
       <c r="F63">
-        <v>0.1457105072723281</v>
+        <v>-0.1417280112946836</v>
       </c>
       <c r="G63">
-        <v>-8.423544318380271</v>
+        <v>-10.43630140371017</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.989922306495012</v>
       </c>
       <c r="E64">
-        <v>-12.81146260706773</v>
+        <v>-17.50778450383239</v>
       </c>
       <c r="F64">
-        <v>0.2649523381705113</v>
+        <v>-0.1923246922576774</v>
       </c>
       <c r="G64">
-        <v>-8.640984308681555</v>
+        <v>-11.38216929898662</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.158125651595211</v>
       </c>
       <c r="E65">
-        <v>-12.37254479234829</v>
+        <v>-18.4860571582874</v>
       </c>
       <c r="F65">
-        <v>-0.03717313444813557</v>
+        <v>-1.111182950139001</v>
       </c>
       <c r="G65">
-        <v>-9.059113653223154</v>
+        <v>-11.52781944278881</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.267674081375594</v>
       </c>
       <c r="E66">
-        <v>-11.62009807970779</v>
+        <v>-16.36697133182007</v>
       </c>
       <c r="F66">
-        <v>-0.06148654608770385</v>
+        <v>-0.8666662885480457</v>
       </c>
       <c r="G66">
-        <v>-8.125002374794194</v>
+        <v>-10.64188634051718</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.319469352863557</v>
       </c>
       <c r="E67">
-        <v>-12.67827112955413</v>
+        <v>-16.08575309594375</v>
       </c>
       <c r="F67">
-        <v>0.0176805265978449</v>
+        <v>-0.9495328500544971</v>
       </c>
       <c r="G67">
-        <v>-8.794670164082826</v>
+        <v>-10.96572650232658</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.309252532750408</v>
       </c>
       <c r="E68">
-        <v>-12.84624581592065</v>
+        <v>-15.98241784756272</v>
       </c>
       <c r="F68">
-        <v>-0.3821185748522945</v>
+        <v>-0.6418763682873578</v>
       </c>
       <c r="G68">
-        <v>-8.393074894979268</v>
+        <v>-11.41555900957553</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.233974054821859</v>
       </c>
       <c r="E69">
-        <v>-13.28046760309414</v>
+        <v>-16.53149984946675</v>
       </c>
       <c r="F69">
-        <v>-0.07695713570238742</v>
+        <v>-1.337439909070047</v>
       </c>
       <c r="G69">
-        <v>-8.574218012389972</v>
+        <v>-10.21404786138118</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.099396546159689</v>
       </c>
       <c r="E70">
-        <v>-12.33821443089614</v>
+        <v>-16.91863003543448</v>
       </c>
       <c r="F70">
-        <v>-0.2195763230749755</v>
+        <v>-1.220814062429904</v>
       </c>
       <c r="G70">
-        <v>-8.198491894061076</v>
+        <v>-11.24320628472258</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.902823482679738</v>
       </c>
       <c r="E71">
-        <v>-11.94778298737683</v>
+        <v>-17.19682325067368</v>
       </c>
       <c r="F71">
-        <v>-0.8227686147714915</v>
+        <v>-1.046258826577187</v>
       </c>
       <c r="G71">
-        <v>-7.914708885049382</v>
+        <v>-11.83946002284019</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.654186582376384</v>
       </c>
       <c r="E72">
-        <v>-12.16722830931453</v>
+        <v>-17.38371337297024</v>
       </c>
       <c r="F72">
-        <v>-0.765597181732478</v>
+        <v>-1.314885121426622</v>
       </c>
       <c r="G72">
-        <v>-8.066199603227385</v>
+        <v>-9.824789985341138</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.356400440447128</v>
       </c>
       <c r="E73">
-        <v>-13.21025814207922</v>
+        <v>-16.78098253949733</v>
       </c>
       <c r="F73">
-        <v>-0.8251253200324561</v>
+        <v>-1.371202507673349</v>
       </c>
       <c r="G73">
-        <v>-8.082736959886986</v>
+        <v>-11.29274288660551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.014396610082891</v>
       </c>
       <c r="E74">
-        <v>-11.76389524334736</v>
+        <v>-17.10618131493615</v>
       </c>
       <c r="F74">
-        <v>-1.014904292013823</v>
+        <v>-1.287446279576291</v>
       </c>
       <c r="G74">
-        <v>-7.744301924581181</v>
+        <v>-9.403760040940988</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.637675402670776</v>
       </c>
       <c r="E75">
-        <v>-11.92942002527572</v>
+        <v>-15.54040255662203</v>
       </c>
       <c r="F75">
-        <v>-1.02609139378863</v>
+        <v>-1.294699464555203</v>
       </c>
       <c r="G75">
-        <v>-7.204823163106637</v>
+        <v>-9.739534005562085</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.226640381772164</v>
       </c>
       <c r="E76">
-        <v>-12.97708701542427</v>
+        <v>-18.30689714112193</v>
       </c>
       <c r="F76">
-        <v>-0.8027701689331058</v>
+        <v>-1.957511843333408</v>
       </c>
       <c r="G76">
-        <v>-6.788911924339222</v>
+        <v>-8.576331119074256</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.793014878966644</v>
       </c>
       <c r="E77">
-        <v>-13.12657647089148</v>
+        <v>-17.82133604412349</v>
       </c>
       <c r="F77">
-        <v>-1.169123936495215</v>
+        <v>-1.716257292574678</v>
       </c>
       <c r="G77">
-        <v>-7.16379476872734</v>
+        <v>-8.648688616903129</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.340237181792761</v>
       </c>
       <c r="E78">
-        <v>-13.05630361124045</v>
+        <v>-17.76003409148165</v>
       </c>
       <c r="F78">
-        <v>-1.000896599232483</v>
+        <v>-1.458446162536193</v>
       </c>
       <c r="G78">
-        <v>-6.287042524379034</v>
+        <v>-9.055323842321995</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.874420471268858</v>
       </c>
       <c r="E79">
-        <v>-13.49946007763107</v>
+        <v>-17.39936377914075</v>
       </c>
       <c r="F79">
-        <v>-1.325231430287588</v>
+        <v>-2.148857258073469</v>
       </c>
       <c r="G79">
-        <v>-5.603393450025608</v>
+        <v>-8.777538906320965</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.405207496097272</v>
       </c>
       <c r="E80">
-        <v>-14.50749386326448</v>
+        <v>-17.72201755218726</v>
       </c>
       <c r="F80">
-        <v>-1.743018529889518</v>
+        <v>-1.760824287212694</v>
       </c>
       <c r="G80">
-        <v>-5.878002163557096</v>
+        <v>-8.521393626504473</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.934197644834585</v>
       </c>
       <c r="E81">
-        <v>-14.28494200815752</v>
+        <v>-20.16139328826909</v>
       </c>
       <c r="F81">
-        <v>-1.358961722562181</v>
+        <v>-1.96360779905061</v>
       </c>
       <c r="G81">
-        <v>-5.133302680868642</v>
+        <v>-7.250382924459527</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.47254963937987</v>
       </c>
       <c r="E82">
-        <v>-15.43074103005228</v>
+        <v>-17.92516489617135</v>
       </c>
       <c r="F82">
-        <v>-1.72685128328908</v>
+        <v>-1.593434429394192</v>
       </c>
       <c r="G82">
-        <v>-5.002496783401378</v>
+        <v>-7.169133316204556</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.023284775011686</v>
       </c>
       <c r="E83">
-        <v>-15.44596575966607</v>
+        <v>-21.08444120220055</v>
       </c>
       <c r="F83">
-        <v>-1.494654101712559</v>
+        <v>-1.734309075016484</v>
       </c>
       <c r="G83">
-        <v>-4.557382672754906</v>
+        <v>-6.239002159527203</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.591547921298884</v>
       </c>
       <c r="E84">
-        <v>-16.05440247038864</v>
+        <v>-20.73045491749497</v>
       </c>
       <c r="F84">
-        <v>-1.597224210262</v>
+        <v>-2.388218989316803</v>
       </c>
       <c r="G84">
-        <v>-4.803497258264176</v>
+        <v>-7.315137831935168</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.18566607312997</v>
       </c>
       <c r="E85">
-        <v>-17.01579297374305</v>
+        <v>-22.89071815811404</v>
       </c>
       <c r="F85">
-        <v>-2.06159455076036</v>
+        <v>-2.218562718284242</v>
       </c>
       <c r="G85">
-        <v>-4.201337321339559</v>
+        <v>-6.471716236187701</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.8077829480866139</v>
       </c>
       <c r="E86">
-        <v>-18.63038415338586</v>
+        <v>-21.50258690664682</v>
       </c>
       <c r="F86">
-        <v>-2.056566360625367</v>
+        <v>-2.870442304080298</v>
       </c>
       <c r="G86">
-        <v>-4.567616802798813</v>
+        <v>-6.103655051421669</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.4679866047762807</v>
       </c>
       <c r="E87">
-        <v>-18.92202240795384</v>
+        <v>-23.77646503164432</v>
       </c>
       <c r="F87">
-        <v>-2.347376334521773</v>
+        <v>-2.640916607377806</v>
       </c>
       <c r="G87">
-        <v>-4.280641165209778</v>
+        <v>-7.573734184256566</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.17138926994655</v>
       </c>
       <c r="E88">
-        <v>-20.52055561876544</v>
+        <v>-25.56634891165004</v>
       </c>
       <c r="F88">
-        <v>-2.679492848958776</v>
+        <v>-2.431773718988598</v>
       </c>
       <c r="G88">
-        <v>-3.690073784054681</v>
+        <v>-6.312934643704612</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.07702464106672612</v>
       </c>
       <c r="E89">
-        <v>-21.94771778770478</v>
+        <v>-26.78944445638173</v>
       </c>
       <c r="F89">
-        <v>-2.276331404220674</v>
+        <v>-2.683295883705029</v>
       </c>
       <c r="G89">
-        <v>-3.311827687568132</v>
+        <v>-5.405178136841112</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.269758074911863</v>
       </c>
       <c r="E90">
-        <v>-24.43850528919569</v>
+        <v>-26.75726059160921</v>
       </c>
       <c r="F90">
-        <v>-3.038158538655503</v>
+        <v>-2.880317271889071</v>
       </c>
       <c r="G90">
-        <v>-4.160233458864395</v>
+        <v>-5.868798337082853</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.405606975801095</v>
       </c>
       <c r="E91">
-        <v>-24.45254355861947</v>
+        <v>-28.24030865827721</v>
       </c>
       <c r="F91">
-        <v>-3.08222851285184</v>
+        <v>-3.221717299809248</v>
       </c>
       <c r="G91">
-        <v>-3.957004439137068</v>
+        <v>-5.525142878275971</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.4803867306209777</v>
       </c>
       <c r="E92">
-        <v>-26.90926335015068</v>
+        <v>-30.30542413152111</v>
       </c>
       <c r="F92">
-        <v>-3.214338202985111</v>
+        <v>-3.972430228800717</v>
       </c>
       <c r="G92">
-        <v>-3.768449042223577</v>
+        <v>-6.963318693888387</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.4930183473701439</v>
       </c>
       <c r="E93">
-        <v>-27.72701065798178</v>
+        <v>-31.86817560496111</v>
       </c>
       <c r="F93">
-        <v>-3.621127896947475</v>
+        <v>-3.779968174801683</v>
       </c>
       <c r="G93">
-        <v>-3.532059997416502</v>
+        <v>-5.824934967276197</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.4457792005679397</v>
       </c>
       <c r="E94">
-        <v>-29.14363506790527</v>
+        <v>-33.06756911673665</v>
       </c>
       <c r="F94">
-        <v>-3.651406382254602</v>
+        <v>-3.754172813878506</v>
       </c>
       <c r="G94">
-        <v>-4.030940204536036</v>
+        <v>-7.134857675794597</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3398950322916712</v>
       </c>
       <c r="E95">
-        <v>-31.77590341858082</v>
+        <v>-34.61373278988655</v>
       </c>
       <c r="F95">
-        <v>-3.472128623838525</v>
+        <v>-4.260639129052333</v>
       </c>
       <c r="G95">
-        <v>-4.125842975699856</v>
+        <v>-6.620076668997994</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.1781007662550479</v>
       </c>
       <c r="E96">
-        <v>-33.19898316820224</v>
+        <v>-36.15247655837489</v>
       </c>
       <c r="F96">
-        <v>-3.834714976452702</v>
+        <v>-4.492196810993892</v>
       </c>
       <c r="G96">
-        <v>-3.714443416576677</v>
+        <v>-6.891499316395261</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.02946391329143722</v>
       </c>
       <c r="E97">
-        <v>-36.58029961177554</v>
+        <v>-37.94334538147727</v>
       </c>
       <c r="F97">
-        <v>-4.193206708994841</v>
+        <v>-4.438161576941877</v>
       </c>
       <c r="G97">
-        <v>-4.273701381611553</v>
+        <v>-6.160282373094566</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2831268888613993</v>
       </c>
       <c r="E98">
-        <v>-37.41301352620199</v>
+        <v>-40.48790624757227</v>
       </c>
       <c r="F98">
-        <v>-4.476892723227172</v>
+        <v>-4.330386007633245</v>
       </c>
       <c r="G98">
-        <v>-5.396243370534744</v>
+        <v>-7.37539418465281</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5599152837227283</v>
       </c>
       <c r="E99">
-        <v>-39.28659719129148</v>
+        <v>-41.66194256914186</v>
       </c>
       <c r="F99">
-        <v>-4.953442549648893</v>
+        <v>-4.793728344184732</v>
       </c>
       <c r="G99">
-        <v>-5.291011313901793</v>
+        <v>-7.818234408758588</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.868095463176443</v>
       </c>
       <c r="E100">
-        <v>-42.6300872914787</v>
+        <v>-45.0147115125708</v>
       </c>
       <c r="F100">
-        <v>-4.971714677819845</v>
+        <v>-4.684798859084</v>
       </c>
       <c r="G100">
-        <v>-5.684803838136991</v>
+        <v>-8.70948637117808</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.165137795875224</v>
       </c>
       <c r="E101">
-        <v>-43.22156486704255</v>
+        <v>-46.59396700953175</v>
       </c>
       <c r="F101">
-        <v>-4.877782784546798</v>
+        <v>-5.178402285227155</v>
       </c>
       <c r="G101">
-        <v>-6.290310621052241</v>
+        <v>-8.705962339223237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.489467799138786</v>
       </c>
       <c r="E102">
-        <v>-46.04471292561542</v>
+        <v>-49.18128799144417</v>
       </c>
       <c r="F102">
-        <v>-4.937217317330259</v>
+        <v>-4.714044370239836</v>
       </c>
       <c r="G102">
-        <v>-7.109447896038257</v>
+        <v>-9.538139188686488</v>
       </c>
     </row>
   </sheetData>
